--- a/Backtest/02-01-19/S&P500stock_02-01-19period252RS90.xlsx
+++ b/Backtest/02-01-19/S&P500stock_02-01-19period252RS90.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="61">
   <si>
     <t>Stock</t>
   </si>
@@ -127,22 +127,46 @@
     <t>EM Rating</t>
   </si>
   <si>
-    <t>MRK</t>
+    <t>DXCM</t>
+  </si>
+  <si>
+    <t>BSX</t>
+  </si>
+  <si>
+    <t>MOH</t>
   </si>
   <si>
     <t>NRG</t>
   </si>
   <si>
-    <t>ORLY</t>
-  </si>
-  <si>
-    <t>2019-02-01</t>
+    <t>DECK</t>
+  </si>
+  <si>
+    <t>AES</t>
+  </si>
+  <si>
+    <t>ERIE</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>2019-02-21</t>
+  </si>
+  <si>
+    <t>2019-02-06</t>
+  </si>
+  <si>
+    <t>2019-02-11</t>
   </si>
   <si>
     <t>2019-02-28</t>
   </si>
   <si>
-    <t>2019-02-06</t>
+    <t>2019-05-23</t>
+  </si>
+  <si>
+    <t>2019-02-27</t>
   </si>
   <si>
     <t>Healthcare</t>
@@ -154,13 +178,25 @@
     <t>Consumer Cyclical</t>
   </si>
   <si>
-    <t>Drug Manufacturers - General</t>
+    <t>Financial Services</t>
+  </si>
+  <si>
+    <t>Medical Devices</t>
+  </si>
+  <si>
+    <t>Healthcare Plans</t>
   </si>
   <si>
     <t>Utilities - Independent Power Producers</t>
   </si>
   <si>
-    <t>Specialty Retail</t>
+    <t>Footwear &amp; Accessories</t>
+  </si>
+  <si>
+    <t>Utilities - Diversified</t>
+  </si>
+  <si>
+    <t>Insurance Brokers</t>
   </si>
 </sst>
 </file>
@@ -518,7 +554,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AK4"/>
+  <dimension ref="A1:AK8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:37">
@@ -639,43 +675,43 @@
         <v>37</v>
       </c>
       <c r="B2">
-        <v>95.4639175257732</v>
+        <v>99.79381443298969</v>
       </c>
       <c r="C2">
-        <v>36</v>
+        <v>166</v>
       </c>
       <c r="D2">
-        <v>72.91</v>
+        <v>35.26</v>
       </c>
       <c r="E2">
-        <v>1.72</v>
+        <v>3.36</v>
       </c>
       <c r="F2">
-        <v>-0.9043734703107533</v>
+        <v>1.231741782487619</v>
       </c>
       <c r="G2">
-        <v>1.44</v>
+        <v>3.68</v>
       </c>
       <c r="H2">
-        <v>-1.152331919396064</v>
+        <v>1.351229803423931</v>
       </c>
       <c r="I2">
-        <v>71.05152587890625</v>
+        <v>35.55299987792969</v>
       </c>
       <c r="J2">
-        <v>72.61068649291992</v>
+        <v>35.00100021362304</v>
       </c>
       <c r="K2">
-        <v>71.35534332275391</v>
+        <v>32.22680004119873</v>
       </c>
       <c r="L2">
-        <v>62.95610677719116</v>
+        <v>29.19218750953674</v>
       </c>
       <c r="M2">
-        <v>0.98</v>
+        <v>1.02</v>
       </c>
       <c r="N2">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -696,52 +732,52 @@
         <v>0</v>
       </c>
       <c r="V2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W2" t="b">
         <v>1</v>
       </c>
       <c r="X2">
-        <v>50.41</v>
+        <v>13.23</v>
       </c>
       <c r="Y2">
-        <v>76.52</v>
+        <v>38.17</v>
       </c>
       <c r="Z2">
-        <v>181.28</v>
+        <v>12.92</v>
       </c>
       <c r="AA2">
-        <v>7.93</v>
+        <v>-134.43</v>
       </c>
       <c r="AB2">
-        <v>92.42</v>
+        <v>173.13</v>
       </c>
       <c r="AC2">
-        <v>297.3</v>
+        <v>630</v>
       </c>
       <c r="AD2">
-        <v>6</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="AE2">
-        <v>14.06</v>
+        <v>55.88</v>
       </c>
       <c r="AF2">
-        <v>137.04</v>
+        <v>221.43</v>
       </c>
       <c r="AG2">
-        <v>172.97</v>
+        <v>-180</v>
       </c>
       <c r="AH2" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="AI2" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="AJ2" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AK2">
-        <v>89.99999999999999</v>
+        <v>82.93847262215566</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -749,46 +785,46 @@
         <v>38</v>
       </c>
       <c r="B3">
-        <v>97.31958762886597</v>
+        <v>95.4639175257732</v>
       </c>
       <c r="C3">
-        <v>165</v>
+        <v>71</v>
       </c>
       <c r="D3">
-        <v>39.6</v>
+        <v>38.15</v>
       </c>
       <c r="E3">
-        <v>2.42</v>
+        <v>1.97</v>
       </c>
       <c r="F3">
-        <v>1.073943495994022</v>
+        <v>-0.186583370601675</v>
       </c>
       <c r="G3">
-        <v>1.96</v>
+        <v>2.4</v>
       </c>
       <c r="H3">
-        <v>0.5121475197315836</v>
+        <v>-0.1434639050548875</v>
       </c>
       <c r="I3">
-        <v>38.23599929809571</v>
+        <v>37.37599945068359</v>
       </c>
       <c r="J3">
-        <v>39.86199989318848</v>
+        <v>36.30099983215332</v>
       </c>
       <c r="K3">
-        <v>38.58120010375976</v>
+        <v>35.72519973754883</v>
       </c>
       <c r="L3">
-        <v>34.47445001602173</v>
+        <v>34.34945002555847</v>
       </c>
       <c r="M3">
-        <v>0.96</v>
+        <v>1.03</v>
       </c>
       <c r="N3">
-        <v>0.99</v>
+        <v>1.05</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q3">
         <v>0</v>
@@ -800,58 +836,58 @@
         <v>0</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>1.111111111111111</v>
       </c>
       <c r="U3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V3" t="b">
         <v>1</v>
       </c>
       <c r="W3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X3">
-        <v>23.75</v>
+        <v>25.04</v>
       </c>
       <c r="Y3">
-        <v>43.08</v>
+        <v>39.44</v>
       </c>
       <c r="Z3">
-        <v>11.18</v>
+        <v>54.05</v>
       </c>
       <c r="AA3">
-        <v>3520</v>
+        <v>-1959.18</v>
       </c>
       <c r="AB3">
-        <v>60.04</v>
+        <v>182.35</v>
       </c>
       <c r="AC3">
-        <v>95.03</v>
+        <v>168.89</v>
       </c>
       <c r="AD3">
-        <v>-30.66</v>
+        <v>5.21</v>
       </c>
       <c r="AE3">
-        <v>-204.35</v>
+        <v>-22.5</v>
       </c>
       <c r="AF3">
-        <v>-73.86</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="AG3">
-        <v>118.22</v>
+        <v>148.89</v>
       </c>
       <c r="AH3" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="AI3" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="AJ3" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="AK3">
-        <v>64.94940969312566</v>
+        <v>67.50689078543792</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -859,43 +895,43 @@
         <v>39</v>
       </c>
       <c r="B4">
-        <v>97.52577319587628</v>
+        <v>97.11340206185567</v>
       </c>
       <c r="C4">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="D4">
-        <v>344.33</v>
+        <v>132.98</v>
       </c>
       <c r="E4">
-        <v>1.98</v>
+        <v>3.16</v>
       </c>
       <c r="F4">
-        <v>-0.1695700256832653</v>
+        <v>1.027666220892037</v>
       </c>
       <c r="G4">
-        <v>2</v>
+        <v>3.49</v>
       </c>
       <c r="H4">
-        <v>0.6401843996644796</v>
+        <v>1.129361206071607</v>
       </c>
       <c r="I4">
-        <v>340.2820007324219</v>
+        <v>134.6060028076172</v>
       </c>
       <c r="J4">
-        <v>341.9250030517578</v>
+        <v>130.4995006561279</v>
       </c>
       <c r="K4">
-        <v>341.5481994628906</v>
+        <v>127.7564002990723</v>
       </c>
       <c r="L4">
-        <v>303.7788510894775</v>
+        <v>118.534999961853</v>
       </c>
       <c r="M4">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="N4">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="P4">
         <v>0</v>
@@ -916,52 +952,495 @@
         <v>1</v>
       </c>
       <c r="V4" t="b">
+        <v>0</v>
+      </c>
+      <c r="W4" t="b">
+        <v>0</v>
+      </c>
+      <c r="X4">
+        <v>71.06999999999999</v>
+      </c>
+      <c r="Y4">
+        <v>154.06</v>
+      </c>
+      <c r="Z4">
+        <v>10.1</v>
+      </c>
+      <c r="AA4">
+        <v>24.96</v>
+      </c>
+      <c r="AB4">
+        <v>136.76</v>
+      </c>
+      <c r="AC4">
+        <v>169.25</v>
+      </c>
+      <c r="AD4">
+        <v>12.62</v>
+      </c>
+      <c r="AE4">
+        <v>-2.13</v>
+      </c>
+      <c r="AF4">
+        <v>83.8</v>
+      </c>
+      <c r="AG4">
+        <v>138.49</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>47</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>51</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>56</v>
+      </c>
+      <c r="AK4">
+        <v>58.71505801675769</v>
+      </c>
+    </row>
+    <row r="5" spans="1:37">
+      <c r="A5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5">
+        <v>98.14432989690721</v>
+      </c>
+      <c r="C5">
+        <v>164</v>
+      </c>
+      <c r="D5">
+        <v>40.91</v>
+      </c>
+      <c r="E5">
+        <v>1.56</v>
+      </c>
+      <c r="F5">
+        <v>-0.6049382718726177</v>
+      </c>
+      <c r="G5">
+        <v>2.05</v>
+      </c>
+      <c r="H5">
+        <v>-0.5521692159670646</v>
+      </c>
+      <c r="I5">
+        <v>40.41800003051758</v>
+      </c>
+      <c r="J5">
+        <v>40.21549987792969</v>
+      </c>
+      <c r="K5">
+        <v>39.76359992980957</v>
+      </c>
+      <c r="L5">
+        <v>35.50505002021789</v>
+      </c>
+      <c r="M5">
+        <v>1.01</v>
+      </c>
+      <c r="N5">
+        <v>1.02</v>
+      </c>
+      <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="Q5">
+        <v>0</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5" t="b">
         <v>1</v>
       </c>
-      <c r="W4" t="b">
+      <c r="V5" t="b">
         <v>1</v>
       </c>
-      <c r="X4">
-        <v>217.64</v>
-      </c>
-      <c r="Y4">
-        <v>363.2</v>
-      </c>
-      <c r="Z4">
-        <v>28.28</v>
-      </c>
-      <c r="AA4">
-        <v>6.02</v>
-      </c>
-      <c r="AB4">
-        <v>3.95</v>
-      </c>
-      <c r="AC4">
-        <v>28.25</v>
-      </c>
-      <c r="AD4">
-        <v>73.47</v>
-      </c>
-      <c r="AE4">
-        <v>5.09</v>
-      </c>
-      <c r="AF4">
-        <v>18.36</v>
-      </c>
-      <c r="AG4">
-        <v>3.11</v>
-      </c>
-      <c r="AH4" t="s">
+      <c r="W5" t="b">
+        <v>0</v>
+      </c>
+      <c r="X5">
+        <v>23.75</v>
+      </c>
+      <c r="Y5">
+        <v>43.08</v>
+      </c>
+      <c r="Z5">
+        <v>11.18</v>
+      </c>
+      <c r="AA5">
+        <v>3520</v>
+      </c>
+      <c r="AB5">
+        <v>60.04</v>
+      </c>
+      <c r="AC5">
+        <v>95.03</v>
+      </c>
+      <c r="AD5">
+        <v>-30.66</v>
+      </c>
+      <c r="AE5">
+        <v>-204.35</v>
+      </c>
+      <c r="AF5">
+        <v>-73.86</v>
+      </c>
+      <c r="AG5">
+        <v>118.22</v>
+      </c>
+      <c r="AH5" t="s">
+        <v>48</v>
+      </c>
+      <c r="AI5" t="s">
+        <v>52</v>
+      </c>
+      <c r="AJ5" t="s">
+        <v>57</v>
+      </c>
+      <c r="AK5">
+        <v>36.11858625799749</v>
+      </c>
+    </row>
+    <row r="6" spans="1:37">
+      <c r="A6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B6">
+        <v>97.31958762886597</v>
+      </c>
+      <c r="C6">
+        <v>169</v>
+      </c>
+      <c r="D6">
+        <v>21.41</v>
+      </c>
+      <c r="E6">
+        <v>2.87</v>
+      </c>
+      <c r="F6">
+        <v>0.7317566565784435</v>
+      </c>
+      <c r="G6">
+        <v>2.8</v>
+      </c>
+      <c r="H6">
+        <v>0.3236278788447431</v>
+      </c>
+      <c r="I6">
+        <v>21.06499977111816</v>
+      </c>
+      <c r="J6">
+        <v>20.25574960708618</v>
+      </c>
+      <c r="K6">
+        <v>20.71686645507813</v>
+      </c>
+      <c r="L6">
+        <v>19.31940826416016</v>
+      </c>
+      <c r="M6">
+        <v>1.04</v>
+      </c>
+      <c r="N6">
+        <v>1.02</v>
+      </c>
+      <c r="P6">
+        <v>1</v>
+      </c>
+      <c r="Q6">
+        <v>0</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>0.5555555555555555</v>
+      </c>
+      <c r="U6" t="b">
+        <v>0</v>
+      </c>
+      <c r="V6" t="b">
+        <v>1</v>
+      </c>
+      <c r="W6" t="b">
+        <v>0</v>
+      </c>
+      <c r="X6">
+        <v>14.05</v>
+      </c>
+      <c r="Y6">
+        <v>22.92</v>
+      </c>
+      <c r="Z6">
+        <v>3.76</v>
+      </c>
+      <c r="AA6">
+        <v>296320</v>
+      </c>
+      <c r="AB6">
+        <v>185.86</v>
+      </c>
+      <c r="AC6">
+        <v>921.1799999999999</v>
+      </c>
+      <c r="AD6">
+        <v>19.29</v>
+      </c>
+      <c r="AE6">
+        <v>170.67</v>
+      </c>
+      <c r="AF6">
+        <v>348.95</v>
+      </c>
+      <c r="AG6">
+        <v>-251.55</v>
+      </c>
+      <c r="AH6" t="s">
+        <v>49</v>
+      </c>
+      <c r="AI6" t="s">
+        <v>53</v>
+      </c>
+      <c r="AJ6" t="s">
+        <v>58</v>
+      </c>
+      <c r="AK6">
+        <v>92.00000000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:37">
+      <c r="A7" t="s">
         <v>42</v>
       </c>
-      <c r="AI4" t="s">
+      <c r="B7">
+        <v>96.70103092783505</v>
+      </c>
+      <c r="C7">
+        <v>103</v>
+      </c>
+      <c r="D7">
+        <v>16.39</v>
+      </c>
+      <c r="E7">
+        <v>1.26</v>
+      </c>
+      <c r="F7">
+        <v>-0.9110516142659906</v>
+      </c>
+      <c r="G7">
+        <v>1.92</v>
+      </c>
+      <c r="H7">
+        <v>-0.7039740457344444</v>
+      </c>
+      <c r="I7">
+        <v>16.09200019836426</v>
+      </c>
+      <c r="J7">
+        <v>15.4595000743866</v>
+      </c>
+      <c r="K7">
+        <v>15.24639999389648</v>
+      </c>
+      <c r="L7">
+        <v>13.90039999485016</v>
+      </c>
+      <c r="M7">
+        <v>1.04</v>
+      </c>
+      <c r="N7">
+        <v>1.06</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <v>0</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7" t="b">
+        <v>0</v>
+      </c>
+      <c r="V7" t="b">
+        <v>1</v>
+      </c>
+      <c r="W7" t="b">
+        <v>0</v>
+      </c>
+      <c r="X7">
+        <v>9.869999999999999</v>
+      </c>
+      <c r="Y7">
+        <v>16.42</v>
+      </c>
+      <c r="Z7">
+        <v>9.31</v>
+      </c>
+      <c r="AA7">
+        <v>-47.59</v>
+      </c>
+      <c r="AB7">
+        <v>87.5</v>
+      </c>
+      <c r="AC7">
+        <v>107.39</v>
+      </c>
+      <c r="AD7">
+        <v>3.36</v>
+      </c>
+      <c r="AE7">
+        <v>-65.91</v>
+      </c>
+      <c r="AF7">
+        <v>-57.69</v>
+      </c>
+      <c r="AG7">
+        <v>151.23</v>
+      </c>
+      <c r="AH7" t="s">
+        <v>50</v>
+      </c>
+      <c r="AI7" t="s">
+        <v>52</v>
+      </c>
+      <c r="AJ7" t="s">
+        <v>59</v>
+      </c>
+      <c r="AK7">
+        <v>44.26091293716502</v>
+      </c>
+    </row>
+    <row r="8" spans="1:37">
+      <c r="A8" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8">
+        <v>90.72164948453609</v>
+      </c>
+      <c r="C8">
+        <v>483</v>
+      </c>
+      <c r="D8">
+        <v>146.38</v>
+      </c>
+      <c r="E8">
+        <v>0.89</v>
+      </c>
+      <c r="F8">
+        <v>-1.288591403217817</v>
+      </c>
+      <c r="G8">
+        <v>1.32</v>
+      </c>
+      <c r="H8">
+        <v>-1.40461172158389</v>
+      </c>
+      <c r="I8">
+        <v>144.2459991455078</v>
+      </c>
+      <c r="J8">
+        <v>139.6824989318848</v>
+      </c>
+      <c r="K8">
+        <v>134.9435995483398</v>
+      </c>
+      <c r="L8">
+        <v>125.2823498535156</v>
+      </c>
+      <c r="M8">
+        <v>1.03</v>
+      </c>
+      <c r="N8">
+        <v>1.07</v>
+      </c>
+      <c r="O8" t="s">
+        <v>44</v>
+      </c>
+      <c r="P8">
+        <v>3</v>
+      </c>
+      <c r="Q8">
+        <v>1</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>2.777777777777778</v>
+      </c>
+      <c r="U8" t="b">
+        <v>1</v>
+      </c>
+      <c r="V8" t="b">
+        <v>1</v>
+      </c>
+      <c r="W8" t="b">
+        <v>1</v>
+      </c>
+      <c r="X8">
+        <v>106.63</v>
+      </c>
+      <c r="Y8">
+        <v>150</v>
+      </c>
+      <c r="Z8">
+        <v>6.67</v>
+      </c>
+      <c r="AA8">
+        <v>6.5</v>
+      </c>
+      <c r="AB8">
+        <v>6.18</v>
+      </c>
+      <c r="AC8">
+        <v>155.88</v>
+      </c>
+      <c r="AD8">
+        <v>8.73</v>
+      </c>
+      <c r="AE8">
+        <v>0.58</v>
+      </c>
+      <c r="AF8">
+        <v>21.83</v>
+      </c>
+      <c r="AG8">
+        <v>108.82</v>
+      </c>
+      <c r="AH8" t="s">
         <v>45</v>
       </c>
-      <c r="AJ4" t="s">
-        <v>48</v>
-      </c>
-      <c r="AK4">
-        <v>0</v>
+      <c r="AI8" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ8" t="s">
+        <v>60</v>
+      </c>
+      <c r="AK8">
+        <v>17.59421438279083</v>
       </c>
     </row>
   </sheetData>
